--- a/Resultados.xlsx
+++ b/Resultados.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Pago Móvil" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Consulta Transferencias" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Limites Transferencias" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Lista de Movimientos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Resultados Anulacion" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -39,27 +40,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -87,12 +73,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,7 +443,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -468,8 +452,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="8" max="9"/>
     <col width="70" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -477,1703 +460,1703 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cuenta Pagadora</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ID Pagador</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Teléfono Pagador</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Teléfono Receptor</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ID Receptor</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ID Consumidor</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Moneda</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Fecha y Hora</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Referencia</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Fecha and Hora</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>01150010231002340000</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>J401228917</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>584149089017</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>584123216544</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>V6049297</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>2026-06-12 09:53:59</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>'584123216544</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>'V6049297</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>2026-06-16 12:52:42</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="K4" s="1" t="n"/>
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>2026-06-16 12:52:42</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="1" t="n"/>
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" s="1" t="inlineStr">
         <is>
           <t>2026-06-16 12:52:43</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K6" s="1" t="n"/>
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="1" t="inlineStr">
         <is>
           <t>2026-06-16 12:52:43</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="K7" s="1" t="n"/>
+      <c r="L7" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" s="1" t="inlineStr">
         <is>
           <t>2026-06-16 12:52:44</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>'584123216544</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>'V6049297</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="1" t="n"/>
+      <c r="L8" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M8" s="1" t="inlineStr">
         <is>
           <t>2026-06-16 14:08:22</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="1" t="n"/>
+      <c r="L9" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M9" s="1" t="inlineStr">
         <is>
           <t>2026-06-16 14:08:22</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="K10" s="1" t="n"/>
+      <c r="L10" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M10" s="1" t="inlineStr">
         <is>
           <t>2026-06-16 14:08:23</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="K11" s="1" t="n"/>
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>2026-06-16 14:08:23</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO DATOSAUTORIZADOS NO PUDO SER RESUELTO</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M12" s="1" t="inlineStr">
         <is>
           <t>2026-06-16 14:08:24</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>'584123216544</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>'V6049297</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="K13" s="1" t="n"/>
+      <c r="L13" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M13" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 10:53:45</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="K14" s="1" t="n"/>
+      <c r="L14" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M14" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 10:53:47</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="K15" s="1" t="n"/>
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M15" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 10:53:48</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="K16" s="1" t="n"/>
+      <c r="L16" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M16" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 10:53:49</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="1" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="K17" s="1" t="n"/>
+      <c r="L17" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M17" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 10:53:50</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>'584123216544</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>'V6049297</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="K18" s="1" t="n"/>
+      <c r="L18" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M18" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 13:52:25</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="1" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="K19" s="1" t="n"/>
+      <c r="L19" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 13:52:26</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="K20" s="1" t="n"/>
+      <c r="L20" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M20" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 13:52:26</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="K21" s="1" t="n"/>
+      <c r="L21" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M21" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 13:52:27</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="1" t="inlineStr">
         <is>
           <t>5000</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="K22" s="1" t="n"/>
+      <c r="L22" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M22" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 13:52:27</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>'584123216544</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>'V6049297</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="K23" s="1" t="n"/>
+      <c r="L23" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M23" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 14:14:18</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="1" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="K24" s="1" t="n"/>
+      <c r="L24" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M24" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 14:14:18</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="1" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="K25" s="1" t="n"/>
+      <c r="L25" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="M25" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 14:14:19</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="1" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="K26" s="1" t="n"/>
+      <c r="L26" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="M26" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 14:14:21</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>'01150010231002340000</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>'584149089017</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>'584125463456</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>'V23947064</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>'TEST</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
         <is>
           <t>CUENTA PAGADORA NO EXISTE</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="K27" s="1" t="n"/>
+      <c r="L27" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="M27" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 14:14:22</t>
         </is>
@@ -2191,7 +2174,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -2211,229 +2194,229 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cuenta Pagadora</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ID Pagador</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Cuenta Receptora</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Teléfono Receptor</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ID Receptor</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ID Consumidor</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Moneda</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Beneficiario</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Fecha y Hora</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Referencia</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Descripcion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>'01150010231002341987</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>'01150040411000167277</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>'J315368919</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>'J1234567</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Jhon Doe</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>OPERACION EXITOSA</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 10:54:15</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>'01317739</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>OPERACION EXITOSA</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>'01150010231002341987</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>'J401228917</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>'01150040411000167277</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>'J315368919</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>'J1234567</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Jhon Doe</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>OPERACION EXITOSA</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>2026-06-17 13:44:16</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>'01317740</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>OPERACION EXITOSA</t>
         </is>
@@ -2450,8 +2433,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AJ12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2791,11 +2774,6 @@
           <t>'0.00</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2838,29 +2816,6 @@
           <t>111.111.11.1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
           <t>2026-06-16T14:45:27.113+00:00</t>
@@ -2876,7 +2831,6 @@
           <t>Internal Server Error</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>/api/qa/v1/consultas-limites-pago-movil</t>
@@ -2939,7 +2893,6 @@
           <t>'01150010241005756715</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>VES</t>
@@ -3035,11 +2988,6 @@
           <t>'0.00</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3097,7 +3045,6 @@
           <t>'01150010241005756715</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>VES</t>
@@ -3193,11 +3140,6 @@
           <t>'0.00</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3255,7 +3197,6 @@
           <t>'01150010241005756715</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>VES</t>
@@ -3351,11 +3292,6 @@
           <t>'0.00</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3413,7 +3349,6 @@
           <t>'01150010241005756715</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>VES</t>
@@ -3509,11 +3444,6 @@
           <t>'0.00</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3571,7 +3501,6 @@
           <t>'01150010241005756715</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>VES</t>
@@ -3667,11 +3596,6 @@
           <t>'0.00</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3729,7 +3653,6 @@
           <t>'01150010241005756715</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>VES</t>
@@ -3825,11 +3748,6 @@
           <t>'0.00</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3887,111 +3805,410 @@
           <t>'01150010241005756715</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>900000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'99999999999.00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>'0.00</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>'990000</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>'99999999999.00</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>'0.00</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>'4000</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>'99999999999.00</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>'0.00</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>'120000</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>'99999999999.00</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>'0.00</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>'0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:49:52</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J501540900</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>usuario_beca</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>terminal_beca</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>J1234567</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>'584120000001</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>111.111.11.1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>OPERACION EXITOSA</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>'01150010241005756715</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>900000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'99999999999.00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>'0.00</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>'990000</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>'99999999999.00</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>'0.00</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>'4000</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>'99999999999.00</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>'0.00</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>'120000</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>'99999999999.00</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>'0.00</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>'0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:50:27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>J501540900</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>usuario_beca</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>terminal_beca</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>J1234567</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>'584120000001</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>111.111.11.1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>OPERACION EXITOSA</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>'01150010241005756715</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>900000</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>'99999999999.00</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>'0</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>'0.00</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>'990000</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>'99999999999.00</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>'0</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>'0.00</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>'4000</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>'99999999999.00</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>'0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>'0.00</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>'120000</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>'99999999999.00</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>'0</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>'0.00</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>VES</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
         <is>
           <t>'0.00</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4005,7 +4222,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AK321"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -4389,24 +4606,9 @@
           <t>'402</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -4878,24 +5080,9 @@
           <t>'450</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -5204,24 +5391,9 @@
           <t>'600</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -5530,24 +5702,9 @@
           <t>'687.97</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -5856,24 +6013,9 @@
           <t>'980.2</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -6019,24 +6161,9 @@
           <t>'1252.44</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -6345,24 +6472,9 @@
           <t>'532.03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6834,24 +6946,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7160,24 +7257,9 @@
           <t>'847.42</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -7323,24 +7405,9 @@
           <t>'379.55</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -7812,24 +7879,9 @@
           <t>'522.97</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -8138,24 +8190,9 @@
           <t>'647.48</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -8464,24 +8501,9 @@
           <t>'519.89</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -8637,11 +8659,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
           <t>0115</t>
@@ -8800,11 +8817,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
           <t>0115</t>
@@ -9116,24 +9128,9 @@
           <t>'525</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -9442,24 +9439,9 @@
           <t>'702.52</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -9768,24 +9750,9 @@
           <t>'801.98</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -10094,24 +10061,9 @@
           <t>'1034.2</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -10257,24 +10209,9 @@
           <t>'879.7</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -10583,24 +10520,9 @@
           <t>'801.58</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -10919,11 +10841,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE43" t="inlineStr">
         <is>
           <t>0115</t>
@@ -11082,11 +10999,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE44" t="inlineStr">
         <is>
           <t>0115</t>
@@ -11245,11 +11157,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE45" t="inlineStr">
         <is>
           <t>0115</t>
@@ -11408,11 +11315,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE46" t="inlineStr">
         <is>
           <t>0115</t>
@@ -11571,11 +11473,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE47" t="inlineStr">
         <is>
           <t>0115</t>
@@ -11734,11 +11631,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE48" t="inlineStr">
         <is>
           <t>0115</t>
@@ -11897,11 +11789,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE49" t="inlineStr">
         <is>
           <t>0115</t>
@@ -12060,11 +11947,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE50" t="inlineStr">
         <is>
           <t>0115</t>
@@ -12223,11 +12105,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE51" t="inlineStr">
         <is>
           <t>0115</t>
@@ -12386,11 +12263,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE52" t="inlineStr">
         <is>
           <t>0115</t>
@@ -12549,11 +12421,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE53" t="inlineStr">
         <is>
           <t>0115</t>
@@ -12712,11 +12579,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE54" t="inlineStr">
         <is>
           <t>0115</t>
@@ -12875,11 +12737,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE55" t="inlineStr">
         <is>
           <t>0115</t>
@@ -13038,11 +12895,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE56" t="inlineStr">
         <is>
           <t>0115</t>
@@ -13201,11 +13053,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE57" t="inlineStr">
         <is>
           <t>0115</t>
@@ -13364,11 +13211,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE58" t="inlineStr">
         <is>
           <t>0115</t>
@@ -13527,11 +13369,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE59" t="inlineStr">
         <is>
           <t>0115</t>
@@ -13690,11 +13527,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE60" t="inlineStr">
         <is>
           <t>0115</t>
@@ -13853,11 +13685,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE61" t="inlineStr">
         <is>
           <t>0115</t>
@@ -14016,11 +13843,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE62" t="inlineStr">
         <is>
           <t>0115</t>
@@ -14179,11 +14001,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE63" t="inlineStr">
         <is>
           <t>0115</t>
@@ -14342,11 +14159,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE64" t="inlineStr">
         <is>
           <t>0115</t>
@@ -14505,11 +14317,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE65" t="inlineStr">
         <is>
           <t>0115</t>
@@ -14668,11 +14475,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE66" t="inlineStr">
         <is>
           <t>0115</t>
@@ -14831,11 +14633,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE67" t="inlineStr">
         <is>
           <t>0115</t>
@@ -14994,11 +14791,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE68" t="inlineStr">
         <is>
           <t>0115</t>
@@ -15157,11 +14949,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE69" t="inlineStr">
         <is>
           <t>0115</t>
@@ -15320,11 +15107,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE70" t="inlineStr">
         <is>
           <t>0115</t>
@@ -15636,24 +15418,9 @@
           <t>'960</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC72" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -15962,24 +15729,9 @@
           <t>'634.5</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC74" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -16288,24 +16040,9 @@
           <t>'964.5</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC76" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -16614,24 +16351,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC78" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -16940,24 +16662,9 @@
           <t>'846.98</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC80" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -17230,24 +16937,9 @@
           <t>'402</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC83" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD83" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -17719,24 +17411,9 @@
           <t>'450</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC86" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -18045,24 +17722,9 @@
           <t>'600</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC88" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -18371,24 +18033,9 @@
           <t>'687.97</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC90" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -18697,24 +18344,9 @@
           <t>'980.2</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC92" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD92" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -18860,24 +18492,9 @@
           <t>'1252.44</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC93" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -19186,24 +18803,9 @@
           <t>'532.03</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC95" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -19675,24 +19277,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC98" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -20001,24 +19588,9 @@
           <t>'847.42</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC100" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -20164,24 +19736,9 @@
           <t>'379.55</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC101" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD101" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -20653,24 +20210,9 @@
           <t>'522.97</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC104" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -20979,24 +20521,9 @@
           <t>'647.48</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC106" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD106" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -21305,24 +20832,9 @@
           <t>'519.89</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC108" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -21478,11 +20990,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE109" t="inlineStr">
         <is>
           <t>0115</t>
@@ -21641,11 +21148,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE110" t="inlineStr">
         <is>
           <t>0115</t>
@@ -21957,24 +21459,9 @@
           <t>'525</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC112" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -22283,24 +21770,9 @@
           <t>'702.52</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC114" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -22609,24 +22081,9 @@
           <t>'801.98</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC116" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -22935,24 +22392,9 @@
           <t>'1034.2</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC118" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -23098,24 +22540,9 @@
           <t>'879.7</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC119" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -23424,24 +22851,9 @@
           <t>'801.58</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC121" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -23760,11 +23172,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE123" t="inlineStr">
         <is>
           <t>0115</t>
@@ -23923,11 +23330,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE124" t="inlineStr">
         <is>
           <t>0115</t>
@@ -24086,11 +23488,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE125" t="inlineStr">
         <is>
           <t>0115</t>
@@ -24249,11 +23646,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE126" t="inlineStr">
         <is>
           <t>0115</t>
@@ -24412,11 +23804,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE127" t="inlineStr">
         <is>
           <t>0115</t>
@@ -24575,11 +23962,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE128" t="inlineStr">
         <is>
           <t>0115</t>
@@ -24738,11 +24120,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE129" t="inlineStr">
         <is>
           <t>0115</t>
@@ -24901,11 +24278,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE130" t="inlineStr">
         <is>
           <t>0115</t>
@@ -25064,11 +24436,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE131" t="inlineStr">
         <is>
           <t>0115</t>
@@ -25227,11 +24594,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD132" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE132" t="inlineStr">
         <is>
           <t>0115</t>
@@ -25390,11 +24752,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE133" t="inlineStr">
         <is>
           <t>0115</t>
@@ -25553,11 +24910,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE134" t="inlineStr">
         <is>
           <t>0115</t>
@@ -25716,11 +25068,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE135" t="inlineStr">
         <is>
           <t>0115</t>
@@ -25879,11 +25226,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE136" t="inlineStr">
         <is>
           <t>0115</t>
@@ -26042,11 +25384,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE137" t="inlineStr">
         <is>
           <t>0115</t>
@@ -26205,11 +25542,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE138" t="inlineStr">
         <is>
           <t>0115</t>
@@ -26368,11 +25700,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE139" t="inlineStr">
         <is>
           <t>0115</t>
@@ -26531,11 +25858,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE140" t="inlineStr">
         <is>
           <t>0115</t>
@@ -26694,11 +26016,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE141" t="inlineStr">
         <is>
           <t>0115</t>
@@ -26857,11 +26174,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE142" t="inlineStr">
         <is>
           <t>0115</t>
@@ -27020,11 +26332,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE143" t="inlineStr">
         <is>
           <t>0115</t>
@@ -27183,11 +26490,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE144" t="inlineStr">
         <is>
           <t>0115</t>
@@ -27346,11 +26648,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE145" t="inlineStr">
         <is>
           <t>0115</t>
@@ -27509,11 +26806,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE146" t="inlineStr">
         <is>
           <t>0115</t>
@@ -27672,11 +26964,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE147" t="inlineStr">
         <is>
           <t>0115</t>
@@ -27835,11 +27122,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE148" t="inlineStr">
         <is>
           <t>0115</t>
@@ -27998,11 +27280,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE149" t="inlineStr">
         <is>
           <t>0115</t>
@@ -28161,11 +27438,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE150" t="inlineStr">
         <is>
           <t>0115</t>
@@ -28477,24 +27749,9 @@
           <t>'960</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC152" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -28803,24 +28060,9 @@
           <t>'634.5</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC154" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -29129,24 +28371,9 @@
           <t>'964.5</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC156" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -29455,24 +28682,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC158" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -29781,24 +28993,9 @@
           <t>'846.98</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC160" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -30071,24 +29268,9 @@
           <t>'402</t>
         </is>
       </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC163" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -30560,24 +29742,9 @@
           <t>'450</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC166" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -30886,24 +30053,9 @@
           <t>'600</t>
         </is>
       </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC168" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE168" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -31212,24 +30364,9 @@
           <t>'687.97</t>
         </is>
       </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC170" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE170" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -31538,24 +30675,9 @@
           <t>'980.2</t>
         </is>
       </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC172" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -31701,24 +30823,9 @@
           <t>'1252.44</t>
         </is>
       </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC173" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD173" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE173" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -32027,24 +31134,9 @@
           <t>'532.03</t>
         </is>
       </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC175" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -32516,24 +31608,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC178" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -32842,24 +31919,9 @@
           <t>'847.42</t>
         </is>
       </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC180" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE180" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -33005,24 +32067,9 @@
           <t>'379.55</t>
         </is>
       </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC181" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -33494,24 +32541,9 @@
           <t>'522.97</t>
         </is>
       </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC184" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE184" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -33820,24 +32852,9 @@
           <t>'647.48</t>
         </is>
       </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC186" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -34146,24 +33163,9 @@
           <t>'519.89</t>
         </is>
       </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC188" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE188" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -34319,11 +33321,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE189" t="inlineStr">
         <is>
           <t>0115</t>
@@ -34482,11 +33479,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE190" t="inlineStr">
         <is>
           <t>0115</t>
@@ -34798,24 +33790,9 @@
           <t>'525</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC192" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -35124,24 +34101,9 @@
           <t>'702.52</t>
         </is>
       </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC194" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -35450,24 +34412,9 @@
           <t>'801.98</t>
         </is>
       </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC196" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -35776,24 +34723,9 @@
           <t>'1034.2</t>
         </is>
       </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC198" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -35939,24 +34871,9 @@
           <t>'879.7</t>
         </is>
       </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC199" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -36265,24 +35182,9 @@
           <t>'801.58</t>
         </is>
       </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC201" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -36601,11 +35503,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE203" t="inlineStr">
         <is>
           <t>0115</t>
@@ -36764,11 +35661,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE204" t="inlineStr">
         <is>
           <t>0115</t>
@@ -36927,11 +35819,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE205" t="inlineStr">
         <is>
           <t>0115</t>
@@ -37090,11 +35977,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE206" t="inlineStr">
         <is>
           <t>0115</t>
@@ -37253,11 +36135,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE207" t="inlineStr">
         <is>
           <t>0115</t>
@@ -37416,11 +36293,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE208" t="inlineStr">
         <is>
           <t>0115</t>
@@ -37579,11 +36451,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE209" t="inlineStr">
         <is>
           <t>0115</t>
@@ -37742,11 +36609,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE210" t="inlineStr">
         <is>
           <t>0115</t>
@@ -37905,11 +36767,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD211" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE211" t="inlineStr">
         <is>
           <t>0115</t>
@@ -38068,11 +36925,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE212" t="inlineStr">
         <is>
           <t>0115</t>
@@ -38231,11 +37083,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE213" t="inlineStr">
         <is>
           <t>0115</t>
@@ -38394,11 +37241,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE214" t="inlineStr">
         <is>
           <t>0115</t>
@@ -38557,11 +37399,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD215" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE215" t="inlineStr">
         <is>
           <t>0115</t>
@@ -38720,11 +37557,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE216" t="inlineStr">
         <is>
           <t>0115</t>
@@ -38883,11 +37715,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE217" t="inlineStr">
         <is>
           <t>0115</t>
@@ -39046,11 +37873,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD218" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE218" t="inlineStr">
         <is>
           <t>0115</t>
@@ -39209,11 +38031,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE219" t="inlineStr">
         <is>
           <t>0115</t>
@@ -39372,11 +38189,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD220" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE220" t="inlineStr">
         <is>
           <t>0115</t>
@@ -39535,11 +38347,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE221" t="inlineStr">
         <is>
           <t>0115</t>
@@ -39698,11 +38505,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE222" t="inlineStr">
         <is>
           <t>0115</t>
@@ -39861,11 +38663,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD223" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE223" t="inlineStr">
         <is>
           <t>0115</t>
@@ -40024,11 +38821,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE224" t="inlineStr">
         <is>
           <t>0115</t>
@@ -40187,11 +38979,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE225" t="inlineStr">
         <is>
           <t>0115</t>
@@ -40350,11 +39137,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD226" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE226" t="inlineStr">
         <is>
           <t>0115</t>
@@ -40513,11 +39295,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE227" t="inlineStr">
         <is>
           <t>0115</t>
@@ -40676,11 +39453,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD228" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE228" t="inlineStr">
         <is>
           <t>0115</t>
@@ -40839,11 +39611,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD229" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE229" t="inlineStr">
         <is>
           <t>0115</t>
@@ -41002,11 +39769,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD230" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE230" t="inlineStr">
         <is>
           <t>0115</t>
@@ -41318,24 +40080,9 @@
           <t>'960</t>
         </is>
       </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC232" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -41644,24 +40391,9 @@
           <t>'634.5</t>
         </is>
       </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC234" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD234" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE234" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -41970,24 +40702,9 @@
           <t>'964.5</t>
         </is>
       </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC236" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD236" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE236" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -42296,24 +41013,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC238" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -42622,24 +41324,9 @@
           <t>'846.98</t>
         </is>
       </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC240" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD240" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE240" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -42920,24 +41607,9 @@
           <t>'402</t>
         </is>
       </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC243" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -43421,24 +42093,9 @@
           <t>'450</t>
         </is>
       </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC246" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -43755,24 +42412,9 @@
           <t>'600</t>
         </is>
       </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC248" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD248" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE248" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -44089,24 +42731,9 @@
           <t>'687.97</t>
         </is>
       </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC250" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE250" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -44423,24 +43050,9 @@
           <t>'980.2</t>
         </is>
       </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC252" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD252" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE252" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -44590,24 +43202,9 @@
           <t>'1252.44</t>
         </is>
       </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC253" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -44924,24 +43521,9 @@
           <t>'532.03</t>
         </is>
       </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC255" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -45425,24 +44007,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC258" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -45759,24 +44326,9 @@
           <t>'847.42</t>
         </is>
       </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC260" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -45926,24 +44478,9 @@
           <t>'379.55</t>
         </is>
       </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC261" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD261" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE261" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -46427,24 +44964,9 @@
           <t>'522.97</t>
         </is>
       </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC264" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD264" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -46761,24 +45283,9 @@
           <t>'647.48</t>
         </is>
       </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC266" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD266" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE266" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -47095,24 +45602,9 @@
           <t>'519.89</t>
         </is>
       </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC268" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -47272,11 +45764,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE269" t="inlineStr">
         <is>
           <t>0115</t>
@@ -47439,11 +45926,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE270" t="inlineStr">
         <is>
           <t>0115</t>
@@ -47763,24 +46245,9 @@
           <t>'525</t>
         </is>
       </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC272" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -48097,24 +46564,9 @@
           <t>'702.52</t>
         </is>
       </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC274" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -48431,24 +46883,9 @@
           <t>'801.98</t>
         </is>
       </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC276" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -48765,24 +47202,9 @@
           <t>'1034.2</t>
         </is>
       </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC278" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD278" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE278" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -48932,24 +47354,9 @@
           <t>'879.7</t>
         </is>
       </c>
-      <c r="AB279" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC279" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD279" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE279" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -49266,24 +47673,9 @@
           <t>'801.58</t>
         </is>
       </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC281" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD281" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE281" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -49610,11 +48002,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD283" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE283" t="inlineStr">
         <is>
           <t>0115</t>
@@ -49777,11 +48164,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD284" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE284" t="inlineStr">
         <is>
           <t>0115</t>
@@ -49944,11 +48326,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD285" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE285" t="inlineStr">
         <is>
           <t>0115</t>
@@ -50111,11 +48488,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD286" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE286" t="inlineStr">
         <is>
           <t>0115</t>
@@ -50278,11 +48650,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD287" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE287" t="inlineStr">
         <is>
           <t>0115</t>
@@ -50445,11 +48812,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD288" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE288" t="inlineStr">
         <is>
           <t>0115</t>
@@ -50612,11 +48974,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD289" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE289" t="inlineStr">
         <is>
           <t>0115</t>
@@ -50779,11 +49136,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD290" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE290" t="inlineStr">
         <is>
           <t>0115</t>
@@ -50946,11 +49298,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD291" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE291" t="inlineStr">
         <is>
           <t>0115</t>
@@ -51113,11 +49460,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD292" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE292" t="inlineStr">
         <is>
           <t>0115</t>
@@ -51280,11 +49622,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD293" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE293" t="inlineStr">
         <is>
           <t>0115</t>
@@ -51447,11 +49784,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD294" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE294" t="inlineStr">
         <is>
           <t>0115</t>
@@ -51614,11 +49946,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD295" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE295" t="inlineStr">
         <is>
           <t>0115</t>
@@ -51781,11 +50108,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD296" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE296" t="inlineStr">
         <is>
           <t>0115</t>
@@ -51948,11 +50270,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD297" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE297" t="inlineStr">
         <is>
           <t>0115</t>
@@ -52115,11 +50432,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD298" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE298" t="inlineStr">
         <is>
           <t>0115</t>
@@ -52282,11 +50594,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD299" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE299" t="inlineStr">
         <is>
           <t>0115</t>
@@ -52449,11 +50756,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD300" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE300" t="inlineStr">
         <is>
           <t>0115</t>
@@ -52616,11 +50918,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD301" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE301" t="inlineStr">
         <is>
           <t>0115</t>
@@ -52783,11 +51080,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD302" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE302" t="inlineStr">
         <is>
           <t>0115</t>
@@ -52950,11 +51242,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD303" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE303" t="inlineStr">
         <is>
           <t>0115</t>
@@ -53117,11 +51404,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD304" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE304" t="inlineStr">
         <is>
           <t>0115</t>
@@ -53284,11 +51566,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD305" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE305" t="inlineStr">
         <is>
           <t>0115</t>
@@ -53451,11 +51728,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD306" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE306" t="inlineStr">
         <is>
           <t>0115</t>
@@ -53618,11 +51890,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD307" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE307" t="inlineStr">
         <is>
           <t>0115</t>
@@ -53785,11 +52052,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD308" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE308" t="inlineStr">
         <is>
           <t>0115</t>
@@ -53952,11 +52214,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD309" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE309" t="inlineStr">
         <is>
           <t>0115</t>
@@ -54119,11 +52376,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD310" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE310" t="inlineStr">
         <is>
           <t>0115</t>
@@ -54443,24 +52695,9 @@
           <t>'960</t>
         </is>
       </c>
-      <c r="AB312" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC312" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD312" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE312" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -54777,24 +53014,9 @@
           <t>'634.5</t>
         </is>
       </c>
-      <c r="AB314" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC314" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD314" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE314" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -55111,24 +53333,9 @@
           <t>'964.5</t>
         </is>
       </c>
-      <c r="AB316" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC316" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD316" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE316" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -55445,24 +53652,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB318" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC318" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD318" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE318" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -55779,24 +53971,9 @@
           <t>'846.98</t>
         </is>
       </c>
-      <c r="AB320" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC320" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD320" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE320" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -55890,7 +54067,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -56173,8 +54350,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:S12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -57072,58 +55249,145 @@
           <t>2026061711140100</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>E123456</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>agencia1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>'J123456789</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OPERACION EXITOSA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>9999999999999.99</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1000000000000000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1000000000000000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1000000000000000</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:52:08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>'J085371427</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026061815520862</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>E123456</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>agencia1</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>0.0.0.0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>'J123456789</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0000</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>OPERACION EXITOSA</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>9999999999999.99</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N12" t="n">
         <v>1000000000000000</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O12" t="n">
         <v>1000000000000000</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>1000000000000000</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>1000000000000000</v>
       </c>
     </row>
@@ -57139,7 +55403,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AK161"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -57523,24 +55787,9 @@
           <t>'402</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -58012,24 +56261,9 @@
           <t>'450</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -58338,24 +56572,9 @@
           <t>'600</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -58664,24 +56883,9 @@
           <t>'687.97</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -58990,24 +57194,9 @@
           <t>'980.2</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -59153,24 +57342,9 @@
           <t>'1252.44</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -59479,24 +57653,9 @@
           <t>'532.03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -59968,24 +58127,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -60294,24 +58438,9 @@
           <t>'847.42</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -60457,24 +58586,9 @@
           <t>'379.55</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -60946,24 +59060,9 @@
           <t>'522.97</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -61272,24 +59371,9 @@
           <t>'647.48</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -61598,24 +59682,9 @@
           <t>'519.89</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -61771,11 +59840,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
           <t>0115</t>
@@ -61934,11 +59998,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
           <t>0115</t>
@@ -62250,24 +60309,9 @@
           <t>'525</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -62576,24 +60620,9 @@
           <t>'702.52</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -62902,24 +60931,9 @@
           <t>'801.98</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -63228,24 +61242,9 @@
           <t>'1034.2</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -63391,24 +61390,9 @@
           <t>'879.7</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -63717,24 +61701,9 @@
           <t>'801.58</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -64053,11 +62022,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE43" t="inlineStr">
         <is>
           <t>0115</t>
@@ -64216,11 +62180,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE44" t="inlineStr">
         <is>
           <t>0115</t>
@@ -64379,11 +62338,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE45" t="inlineStr">
         <is>
           <t>0115</t>
@@ -64542,11 +62496,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE46" t="inlineStr">
         <is>
           <t>0115</t>
@@ -64705,11 +62654,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE47" t="inlineStr">
         <is>
           <t>0115</t>
@@ -64868,11 +62812,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE48" t="inlineStr">
         <is>
           <t>0115</t>
@@ -65031,11 +62970,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE49" t="inlineStr">
         <is>
           <t>0115</t>
@@ -65194,11 +63128,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE50" t="inlineStr">
         <is>
           <t>0115</t>
@@ -65357,11 +63286,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE51" t="inlineStr">
         <is>
           <t>0115</t>
@@ -65520,11 +63444,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE52" t="inlineStr">
         <is>
           <t>0115</t>
@@ -65683,11 +63602,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE53" t="inlineStr">
         <is>
           <t>0115</t>
@@ -65846,11 +63760,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE54" t="inlineStr">
         <is>
           <t>0115</t>
@@ -66009,11 +63918,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE55" t="inlineStr">
         <is>
           <t>0115</t>
@@ -66172,11 +64076,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE56" t="inlineStr">
         <is>
           <t>0115</t>
@@ -66335,11 +64234,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE57" t="inlineStr">
         <is>
           <t>0115</t>
@@ -66498,11 +64392,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE58" t="inlineStr">
         <is>
           <t>0115</t>
@@ -66661,11 +64550,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE59" t="inlineStr">
         <is>
           <t>0115</t>
@@ -66824,11 +64708,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE60" t="inlineStr">
         <is>
           <t>0115</t>
@@ -66987,11 +64866,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE61" t="inlineStr">
         <is>
           <t>0115</t>
@@ -67150,11 +65024,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE62" t="inlineStr">
         <is>
           <t>0115</t>
@@ -67313,11 +65182,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE63" t="inlineStr">
         <is>
           <t>0115</t>
@@ -67476,11 +65340,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE64" t="inlineStr">
         <is>
           <t>0115</t>
@@ -67639,11 +65498,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE65" t="inlineStr">
         <is>
           <t>0115</t>
@@ -67802,11 +65656,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE66" t="inlineStr">
         <is>
           <t>0115</t>
@@ -67965,11 +65814,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE67" t="inlineStr">
         <is>
           <t>0115</t>
@@ -68128,11 +65972,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE68" t="inlineStr">
         <is>
           <t>0115</t>
@@ -68291,11 +66130,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE69" t="inlineStr">
         <is>
           <t>0115</t>
@@ -68454,11 +66288,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE70" t="inlineStr">
         <is>
           <t>0115</t>
@@ -68770,24 +66599,9 @@
           <t>'960</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC72" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -69096,24 +66910,9 @@
           <t>'634.5</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC74" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -69422,24 +67221,9 @@
           <t>'964.5</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC76" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -69748,24 +67532,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC78" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -70074,24 +67843,9 @@
           <t>'846.98</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC80" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -70372,24 +68126,9 @@
           <t>'402</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC83" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD83" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -70873,24 +68612,9 @@
           <t>'450</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC86" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -71207,24 +68931,9 @@
           <t>'600</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC88" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -71541,24 +69250,9 @@
           <t>'687.97</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC90" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -71875,24 +69569,9 @@
           <t>'980.2</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC92" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD92" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -72042,24 +69721,9 @@
           <t>'1252.44</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC93" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -72376,24 +70040,9 @@
           <t>'532.03</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC95" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -72877,24 +70526,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC98" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -73211,24 +70845,9 @@
           <t>'847.42</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC100" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -73378,24 +70997,9 @@
           <t>'379.55</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC101" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD101" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE101" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -73879,24 +71483,9 @@
           <t>'522.97</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC104" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -74213,24 +71802,9 @@
           <t>'647.48</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC106" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD106" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -74547,24 +72121,9 @@
           <t>'519.89</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC108" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -74724,11 +72283,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE109" t="inlineStr">
         <is>
           <t>0115</t>
@@ -74891,11 +72445,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE110" t="inlineStr">
         <is>
           <t>0115</t>
@@ -75215,24 +72764,9 @@
           <t>'525</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC112" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -75549,24 +73083,9 @@
           <t>'702.52</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC114" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -75883,24 +73402,9 @@
           <t>'801.98</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC116" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -76217,24 +73721,9 @@
           <t>'1034.2</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC118" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -76384,24 +73873,9 @@
           <t>'879.7</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC119" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -76718,24 +74192,9 @@
           <t>'801.58</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC121" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -77062,11 +74521,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE123" t="inlineStr">
         <is>
           <t>0115</t>
@@ -77229,11 +74683,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE124" t="inlineStr">
         <is>
           <t>0115</t>
@@ -77396,11 +74845,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE125" t="inlineStr">
         <is>
           <t>0115</t>
@@ -77563,11 +75007,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE126" t="inlineStr">
         <is>
           <t>0115</t>
@@ -77730,11 +75169,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE127" t="inlineStr">
         <is>
           <t>0115</t>
@@ -77897,11 +75331,6 @@
           <t>'000006049297</t>
         </is>
       </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE128" t="inlineStr">
         <is>
           <t>0115</t>
@@ -78064,11 +75493,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE129" t="inlineStr">
         <is>
           <t>0115</t>
@@ -78231,11 +75655,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE130" t="inlineStr">
         <is>
           <t>0115</t>
@@ -78398,11 +75817,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE131" t="inlineStr">
         <is>
           <t>0115</t>
@@ -78565,11 +75979,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD132" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE132" t="inlineStr">
         <is>
           <t>0115</t>
@@ -78732,11 +76141,6 @@
           <t>'000412438905</t>
         </is>
       </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE133" t="inlineStr">
         <is>
           <t>0115</t>
@@ -78899,11 +76303,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE134" t="inlineStr">
         <is>
           <t>0115</t>
@@ -79066,11 +76465,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE135" t="inlineStr">
         <is>
           <t>0115</t>
@@ -79233,11 +76627,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE136" t="inlineStr">
         <is>
           <t>0115</t>
@@ -79400,11 +76789,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE137" t="inlineStr">
         <is>
           <t>0115</t>
@@ -79567,11 +76951,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE138" t="inlineStr">
         <is>
           <t>0115</t>
@@ -79734,11 +77113,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE139" t="inlineStr">
         <is>
           <t>0115</t>
@@ -79901,11 +77275,6 @@
           <t>'000081180091</t>
         </is>
       </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE140" t="inlineStr">
         <is>
           <t>0115</t>
@@ -80068,11 +77437,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE141" t="inlineStr">
         <is>
           <t>0115</t>
@@ -80235,11 +77599,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE142" t="inlineStr">
         <is>
           <t>0115</t>
@@ -80402,11 +77761,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE143" t="inlineStr">
         <is>
           <t>0115</t>
@@ -80569,11 +77923,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE144" t="inlineStr">
         <is>
           <t>0115</t>
@@ -80736,11 +78085,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE145" t="inlineStr">
         <is>
           <t>0115</t>
@@ -80903,11 +78247,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE146" t="inlineStr">
         <is>
           <t>0115</t>
@@ -81070,11 +78409,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE147" t="inlineStr">
         <is>
           <t>0115</t>
@@ -81237,11 +78571,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE148" t="inlineStr">
         <is>
           <t>0115</t>
@@ -81404,11 +78733,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE149" t="inlineStr">
         <is>
           <t>0115</t>
@@ -81571,11 +78895,6 @@
           <t>'000000020297</t>
         </is>
       </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
       <c r="AE150" t="inlineStr">
         <is>
           <t>0115</t>
@@ -81895,24 +79214,9 @@
           <t>'960</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC152" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -82229,24 +79533,9 @@
           <t>'634.5</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC154" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -82563,24 +79852,9 @@
           <t>'964.5</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC156" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -82897,24 +80171,9 @@
           <t>'702.97</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC158" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -83231,24 +80490,9 @@
           <t>'846.98</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="AC160" t="inlineStr">
         <is>
           <t>'000000000000</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>              </t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>    </t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -83327,6 +80571,90 @@
       <c r="AK161" t="inlineStr">
         <is>
           <t>ESTIMADO USUARIO, EL PARAMETRO CUENTA NO FUE ENVIADO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>AnulacionRealizada</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Codigo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fallido</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Sin descripción (Código: 0036)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0036</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Fallido</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Sin descripción (Código: 0036)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>0036</t>
         </is>
       </c>
     </row>

--- a/Resultados.xlsx
+++ b/Resultados.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" firstSheet="4" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" firstSheet="4" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Limites Pago Móvil" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,17 @@
     <sheet name="Lista de Movimientos" sheetId="4" r:id="rId4"/>
     <sheet name="Pago Móvil" sheetId="5" r:id="rId5"/>
     <sheet name="Transferencias" sheetId="6" r:id="rId6"/>
-    <sheet name="Listar Bancos" sheetId="10" r:id="rId7"/>
-    <sheet name="Debito Inmediato" sheetId="7" r:id="rId8"/>
-    <sheet name="Cobro_Comercio_C2P_Resultados" sheetId="8" r:id="rId9"/>
-    <sheet name="Anulaciones_Resultados" sheetId="9" r:id="rId10"/>
+    <sheet name="Listar Bancos" sheetId="7" r:id="rId7"/>
+    <sheet name="Debito Inmediato" sheetId="8" r:id="rId8"/>
+    <sheet name="Cobro_Comercio_C2P_Resultados" sheetId="9" r:id="rId9"/>
+    <sheet name="Anulaciones_Resultados" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="107">
   <si>
     <t>Fecha, Hora y Día Ejecución</t>
   </si>
@@ -331,147 +331,6 @@
   </si>
   <si>
     <t>Descripcion</t>
-  </si>
-  <si>
-    <t>Estado_Paso_Previa_OTP</t>
-  </si>
-  <si>
-    <t>Env_datosPeticion_ipCliente</t>
-  </si>
-  <si>
-    <t>Env_datosPeticion_ipConsumidor</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_otp</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_monto</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_concepto</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_cobrador_cuenta</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_cobrador_telefono</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_cobrador_nombre</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_pagador_pagadorId</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_pagador_bancoCodigo</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_pagador_cuenta</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_pagador_telefono</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_pagador_nombre</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_notificar</t>
-  </si>
-  <si>
-    <t>Env_debitoInmediato_subproducto</t>
-  </si>
-  <si>
-    <t>Res_code</t>
-  </si>
-  <si>
-    <t>Res_description</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_monto</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_estatus</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_referencia</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_fechaOperacion</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_horaOperacion</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_concepto</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_cobrador_cuenta</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_cobrador_telefono</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_cobrador_nombre</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_pagador_pagadorId</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_pagador_bancoCodigo</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_pagador_cuenta</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_pagador_telefono</t>
-  </si>
-  <si>
-    <t>Res_debitoInmediato_pagador_nombre</t>
-  </si>
-  <si>
-    <t>Env_idPagador</t>
-  </si>
-  <si>
-    <t>Env_otp</t>
-  </si>
-  <si>
-    <t>Res_Resultado_Cobro</t>
-  </si>
-  <si>
-    <t>Env_telfPagador</t>
-  </si>
-  <si>
-    <t>Env_telfReceptor</t>
-  </si>
-  <si>
-    <t>Env_ctaReceptor</t>
-  </si>
-  <si>
-    <t>Env_moneda</t>
-  </si>
-  <si>
-    <t>Env_concepto</t>
-  </si>
-  <si>
-    <t>Env_codBanco</t>
-  </si>
-  <si>
-    <t>Env_envioEMailPagador</t>
-  </si>
-  <si>
-    <t>Env_envioEMailReceptor</t>
-  </si>
-  <si>
-    <t>Res_datos_referencia</t>
-  </si>
-  <si>
-    <t>Res_datos_serialTransaccion</t>
-  </si>
-  <si>
-    <t>Env_serialOperacion</t>
-  </si>
-  <si>
-    <t>Res_datos_anulacionRealizada</t>
   </si>
   <si>
     <t>Env_tipoPersonaBeneficiario</t>
@@ -965,72 +824,9 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J1" t="s">
-        <v>137</v>
-      </c>
-      <c r="K1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L1" t="s">
-        <v>139</v>
-      </c>
-      <c r="M1" t="s">
-        <v>146</v>
-      </c>
-      <c r="N1" t="s">
-        <v>57</v>
-      </c>
-      <c r="O1" t="s">
-        <v>141</v>
-      </c>
-      <c r="P1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" t="s">
-        <v>147</v>
-      </c>
-      <c r="S1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1463,7 +1259,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -1472,7 +1268,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="J1" t="s">
         <v>63</v>
@@ -1484,10 +1280,10 @@
         <v>9</v>
       </c>
       <c r="M1" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="N1" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="O1" t="s">
         <v>29</v>
@@ -1496,10 +1292,10 @@
         <v>30</v>
       </c>
       <c r="Q1" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="R1" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1509,225 +1305,18 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AO1"/>
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" t="s">
-        <v>103</v>
-      </c>
-      <c r="K1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L1" t="s">
-        <v>105</v>
-      </c>
-      <c r="M1" t="s">
-        <v>106</v>
-      </c>
-      <c r="N1" t="s">
-        <v>107</v>
-      </c>
-      <c r="O1" t="s">
-        <v>108</v>
-      </c>
-      <c r="P1" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>110</v>
-      </c>
-      <c r="R1" t="s">
-        <v>111</v>
-      </c>
-      <c r="S1" t="s">
-        <v>112</v>
-      </c>
-      <c r="T1" t="s">
-        <v>113</v>
-      </c>
-      <c r="U1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V1" t="s">
-        <v>115</v>
-      </c>
-      <c r="W1" t="s">
-        <v>116</v>
-      </c>
-      <c r="X1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>124</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>127</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" t="s">
-        <v>136</v>
-      </c>
-      <c r="M1" t="s">
-        <v>137</v>
-      </c>
-      <c r="N1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O1" t="s">
-        <v>139</v>
-      </c>
-      <c r="P1" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>57</v>
-      </c>
-      <c r="R1" t="s">
-        <v>141</v>
-      </c>
-      <c r="S1" t="s">
-        <v>142</v>
-      </c>
-      <c r="T1" t="s">
-        <v>143</v>
-      </c>
-      <c r="U1" t="s">
-        <v>8</v>
-      </c>
-      <c r="V1" t="s">
-        <v>9</v>
-      </c>
-      <c r="W1" t="s">
-        <v>144</v>
-      </c>
-      <c r="X1" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>